--- a/Result/profitability/4155.xlsx
+++ b/Result/profitability/4155.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM58"/>
+  <dimension ref="A1:AM59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>7.3</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0475</v>
+        <v>1.11125</v>
       </c>
       <c r="N2" t="n">
-        <v>26.98</v>
+        <v>29.94875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.72</v>
       </c>
       <c r="M3" t="n">
-        <v>1.28375</v>
+        <v>1.29125</v>
       </c>
       <c r="N3" t="n">
-        <v>29.9575</v>
+        <v>30.515</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.84</v>
       </c>
       <c r="M4" t="n">
-        <v>1.47875</v>
+        <v>1.5</v>
       </c>
       <c r="N4" t="n">
-        <v>30.285</v>
+        <v>30.8675</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.21</v>
       </c>
       <c r="M5" t="n">
-        <v>1.60875</v>
+        <v>1.7225</v>
       </c>
       <c r="N5" t="n">
-        <v>29.75875</v>
+        <v>30.57</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>99.40000000000001</v>
@@ -7800,6 +7800,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4155</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>436</v>
+      </c>
+      <c r="D59" t="n">
+        <v>306</v>
+      </c>
+      <c r="E59" t="n">
+        <v>130</v>
+      </c>
+      <c r="F59" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="G59" t="n">
+        <v>52</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>11.85%</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>12</v>
+      </c>
+      <c r="J59" t="n">
+        <v>64</v>
+      </c>
+      <c r="K59" t="n">
+        <v>48</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.1775000000000001</v>
+      </c>
+      <c r="N59" t="n">
+        <v>25.54625</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W59" t="n">
+        <v>-0.04999999999999999</v>
+      </c>
+      <c r="X59" t="n">
+        <v>-0.1282051282051282</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>-2.109999999999999</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-0.06602002503128912</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0.9099999999999999</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>-1.596491228070176</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>6.490000000000002</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.2778253424657535</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK59" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
